--- a/survey_templates/048_family_cruise_participation_survey--survey_templates.xlsx
+++ b/survey_templates/048_family_cruise_participation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'4-person_cabin'}</t>
+          <t>4-person_cabin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '4-person cabin'}</t>
+          <t>4-person cabin</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'3-person_cabin'}</t>
+          <t>3-person_cabin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '3-person cabin'}</t>
+          <t>3-person cabin</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'2-person_cabin'}</t>
+          <t>2-person_cabin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '2-person cabin'}</t>
+          <t>2-person cabin</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'1-person_cabin'}</t>
+          <t>1-person_cabin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '1-person cabin'}</t>
+          <t>1-person cabin</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'walker'}</t>
+          <t>walker</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Walker'}</t>
+          <t>Walker</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'medical_condition'}</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Condition'}</t>
+          <t>Medical Condition</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'balcony'}</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Balcony'}</t>
+          <t>Balcony</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'balcony_suite'}</t>
+          <t>balcony_suite</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Balcony Suite'}</t>
+          <t>Balcony Suite</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'non-smoking'}</t>
+          <t>non-smoking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Non-smoking'}</t>
+          <t>Non-smoking</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'starboard'}</t>
+          <t>starboard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Starboard'}</t>
+          <t>Starboard</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'center_deck'}</t>
+          <t>center_deck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Center Deck'}</t>
+          <t>Center Deck</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'aft_deck'}</t>
+          <t>aft_deck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Aft Deck'}</t>
+          <t>Aft Deck</t>
         </is>
       </c>
     </row>
